--- a/importaciones/mass-notification-import-valid.xlsx
+++ b/importaciones/mass-notification-import-valid.xlsx
@@ -1,104 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Polizas" sheetId="1" r:id="Re3fa25a59491441c"/>
-  </x:sheets>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\importaciones\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C6640A-5707-4CA7-AE2C-406CA07EFF5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Polizas" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="0"/>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>poliza</t>
+  </si>
+  <si>
+    <t>IN-GL-000499</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>Inmueble ubicado en panamá</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Arial"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF111827"/>
-      <x:name val="Arial"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="3">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF0B5C8E"/>
-      </x:patternFill>
-    </x:fill>
-  </x:fills>
-  <x:borders count="3">
-    <x:border/>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB7C8D9"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB7C8D9"/>
-      </x:right>
-      <x:top style="thin">
-        <x:color rgb="FFB7C8D9"/>
-      </x:top>
-    </x:border>
-    <x:border>
-      <x:left style="thin">
-        <x:color rgb="FFB7C8D9"/>
-      </x:left>
-      <x:right style="thin">
-        <x:color rgb="FFB7C8D9"/>
-      </x:right>
-      <x:bottom style="thin">
-        <x:color rgb="FFB7C8D9"/>
-      </x:bottom>
-    </x:border>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="10">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="center"/>
-    </x:xf>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0B5C8E"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="3">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C8D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C8D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB7C8D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7C8D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7C8D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7C8D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -289,27 +321,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="8" t="str">
-        <x:v>poliza</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="9" t="str">
-        <x:v>IN-GL-000499</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="24" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="21.95" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>